--- a/Monthly Dept Head Tracking Tool/Department Head Monthly Report Generation.xlsx
+++ b/Monthly Dept Head Tracking Tool/Department Head Monthly Report Generation.xlsx
@@ -1,29 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AdoptionsFosterMgr\Desktop\SPCAAutomation\Monthly Dept Head Tracking Tool\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0511EF6E-6AD9-47DF-AB14-CAB58236178A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4050" yWindow="1065" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Outcomes" sheetId="1" r:id="rId1"/>
     <sheet name="Fosters" sheetId="2" r:id="rId2"/>
-    <sheet name="Uncounted Outcomes" sheetId="3" r:id="rId3"/>
-    <sheet name="Uncounted Fosters" sheetId="4" r:id="rId4"/>
+    <sheet name="Medical_Surgery" sheetId="3" r:id="rId3"/>
+    <sheet name="Uncounted Outcomes" sheetId="4" r:id="rId4"/>
+    <sheet name="Uncounted Fosters" sheetId="5" r:id="rId5"/>
+    <sheet name="Uncounted_Medical_Surgery" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="149">
   <si>
     <t>Category</t>
   </si>
@@ -184,6 +180,42 @@
     <t>Other - Trocaire College Program</t>
   </si>
   <si>
+    <t>Cat Spay</t>
+  </si>
+  <si>
+    <t>Dog Spay</t>
+  </si>
+  <si>
+    <t>Rabbit Spay</t>
+  </si>
+  <si>
+    <t>Cat Neuter</t>
+  </si>
+  <si>
+    <t>Dog Neuter</t>
+  </si>
+  <si>
+    <t>Rabbit Neuter</t>
+  </si>
+  <si>
+    <t>Rat Neuter</t>
+  </si>
+  <si>
+    <t>Cat Dental</t>
+  </si>
+  <si>
+    <t>Dog Dental</t>
+  </si>
+  <si>
+    <t>Cat Other Surgeries</t>
+  </si>
+  <si>
+    <t>Dog Other Surgeries</t>
+  </si>
+  <si>
+    <t>Others Other Surgeries</t>
+  </si>
+  <si>
     <t>AnimalNumber</t>
   </si>
   <si>
@@ -425,16 +457,25 @@
   </si>
   <si>
     <t>Event Hold!</t>
+  </si>
+  <si>
+    <t>Record #</t>
+  </si>
+  <si>
+    <t>Record Subtype</t>
+  </si>
+  <si>
+    <t>Name</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -498,21 +539,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -550,7 +583,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -584,7 +617,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -619,10 +651,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -795,11 +826,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -807,7 +838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -815,7 +846,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -823,15 +854,15 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -839,7 +870,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -847,7 +878,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -855,7 +886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -863,7 +894,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -871,15 +902,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>10</v>
       </c>
       <c r="B12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -887,7 +918,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -895,15 +926,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
         <v>13</v>
       </c>
       <c r="B16">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>14</v>
       </c>
@@ -911,7 +942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -919,15 +950,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
         <v>16</v>
       </c>
       <c r="B20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22" t="s">
         <v>17</v>
       </c>
@@ -935,7 +966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -943,7 +974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
         <v>19</v>
       </c>
@@ -951,7 +982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
         <v>20</v>
       </c>
@@ -959,7 +990,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -967,15 +998,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2">
       <c r="A28" t="s">
         <v>22</v>
       </c>
       <c r="B28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
       <c r="A30" t="s">
         <v>23</v>
       </c>
@@ -983,7 +1014,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2">
       <c r="A31" t="s">
         <v>24</v>
       </c>
@@ -991,12 +1022,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2">
       <c r="A32" t="s">
         <v>25</v>
       </c>
       <c r="B32">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1005,15 +1036,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="34.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1021,7 +1048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -1029,7 +1056,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>27</v>
       </c>
@@ -1037,7 +1064,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -1045,7 +1072,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>29</v>
       </c>
@@ -1053,7 +1080,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>30</v>
       </c>
@@ -1061,7 +1088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -1069,7 +1096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>32</v>
       </c>
@@ -1077,7 +1104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>33</v>
       </c>
@@ -1085,7 +1112,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>34</v>
       </c>
@@ -1093,7 +1120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -1101,7 +1128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -1109,7 +1136,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -1117,15 +1144,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
         <v>38</v>
       </c>
       <c r="B15">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
         <v>39</v>
       </c>
@@ -1133,7 +1160,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1141,7 +1168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>41</v>
       </c>
@@ -1149,7 +1176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -1157,7 +1184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
         <v>43</v>
       </c>
@@ -1165,7 +1192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2">
       <c r="A22" t="s">
         <v>44</v>
       </c>
@@ -1173,7 +1200,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
         <v>45</v>
       </c>
@@ -1181,7 +1208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
         <v>46</v>
       </c>
@@ -1189,7 +1216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
         <v>47</v>
       </c>
@@ -1197,7 +1224,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
         <v>48</v>
       </c>
@@ -1205,7 +1232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2">
       <c r="A27" t="s">
         <v>49</v>
       </c>
@@ -1213,7 +1240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2">
       <c r="A28" t="s">
         <v>50</v>
       </c>
@@ -1221,7 +1248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2">
       <c r="A29" t="s">
         <v>51</v>
       </c>
@@ -1229,7 +1256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2">
       <c r="A30" t="s">
         <v>52</v>
       </c>
@@ -1243,876 +1270,112 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D62"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B6">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
         <v>57</v>
       </c>
-      <c r="B2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B7">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
         <v>58</v>
       </c>
-      <c r="B3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
         <v>59</v>
       </c>
-      <c r="B4" t="s">
-        <v>119</v>
-      </c>
-      <c r="C4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
         <v>60</v>
       </c>
-      <c r="B5" t="s">
-        <v>118</v>
-      </c>
-      <c r="C5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D5" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
         <v>61</v>
       </c>
-      <c r="B6" t="s">
-        <v>118</v>
-      </c>
-      <c r="C6" t="s">
-        <v>122</v>
-      </c>
-      <c r="D6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
         <v>62</v>
       </c>
-      <c r="B7" t="s">
-        <v>119</v>
-      </c>
-      <c r="C7" t="s">
-        <v>122</v>
-      </c>
-      <c r="D7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="B14">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
         <v>63</v>
       </c>
-      <c r="B8" t="s">
-        <v>120</v>
-      </c>
-      <c r="C8" t="s">
-        <v>122</v>
-      </c>
-      <c r="D8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B15">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
         <v>64</v>
       </c>
-      <c r="B9" t="s">
-        <v>119</v>
-      </c>
-      <c r="C9" t="s">
-        <v>122</v>
-      </c>
-      <c r="D9" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B10" t="s">
-        <v>118</v>
-      </c>
-      <c r="C10" t="s">
-        <v>122</v>
-      </c>
-      <c r="D10" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>66</v>
-      </c>
-      <c r="B11" t="s">
-        <v>119</v>
-      </c>
-      <c r="C11" t="s">
-        <v>122</v>
-      </c>
-      <c r="D11" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>67</v>
-      </c>
-      <c r="B12" t="s">
-        <v>118</v>
-      </c>
-      <c r="C12" t="s">
-        <v>122</v>
-      </c>
-      <c r="D12" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>68</v>
-      </c>
-      <c r="B13" t="s">
-        <v>119</v>
-      </c>
-      <c r="C13" t="s">
-        <v>122</v>
-      </c>
-      <c r="D13" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>69</v>
-      </c>
-      <c r="B14" t="s">
-        <v>119</v>
-      </c>
-      <c r="C14" t="s">
-        <v>122</v>
-      </c>
-      <c r="D14" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>70</v>
-      </c>
-      <c r="B15" t="s">
-        <v>119</v>
-      </c>
-      <c r="C15" t="s">
-        <v>122</v>
-      </c>
-      <c r="D15" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>71</v>
-      </c>
-      <c r="B16" t="s">
-        <v>119</v>
-      </c>
-      <c r="C16" t="s">
-        <v>122</v>
-      </c>
-      <c r="D16" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>72</v>
-      </c>
-      <c r="B17" t="s">
-        <v>121</v>
-      </c>
-      <c r="C17" t="s">
-        <v>122</v>
-      </c>
-      <c r="D17" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>73</v>
-      </c>
-      <c r="B18" t="s">
-        <v>118</v>
-      </c>
-      <c r="C18" t="s">
-        <v>122</v>
-      </c>
-      <c r="D18" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>74</v>
-      </c>
-      <c r="B19" t="s">
-        <v>119</v>
-      </c>
-      <c r="C19" t="s">
-        <v>122</v>
-      </c>
-      <c r="D19" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>75</v>
-      </c>
-      <c r="B20" t="s">
-        <v>119</v>
-      </c>
-      <c r="C20" t="s">
-        <v>122</v>
-      </c>
-      <c r="D20" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>76</v>
-      </c>
-      <c r="B21" t="s">
-        <v>119</v>
-      </c>
-      <c r="C21" t="s">
-        <v>122</v>
-      </c>
-      <c r="D21" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>77</v>
-      </c>
-      <c r="B22" t="s">
-        <v>119</v>
-      </c>
-      <c r="C22" t="s">
-        <v>122</v>
-      </c>
-      <c r="D22" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>78</v>
-      </c>
-      <c r="B23" t="s">
-        <v>119</v>
-      </c>
-      <c r="C23" t="s">
-        <v>122</v>
-      </c>
-      <c r="D23" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>79</v>
-      </c>
-      <c r="B24" t="s">
-        <v>118</v>
-      </c>
-      <c r="C24" t="s">
-        <v>122</v>
-      </c>
-      <c r="D24" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>80</v>
-      </c>
-      <c r="B25" t="s">
-        <v>118</v>
-      </c>
-      <c r="C25" t="s">
-        <v>122</v>
-      </c>
-      <c r="D25" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>81</v>
-      </c>
-      <c r="B26" t="s">
-        <v>118</v>
-      </c>
-      <c r="C26" t="s">
-        <v>122</v>
-      </c>
-      <c r="D26" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>82</v>
-      </c>
-      <c r="B27" t="s">
-        <v>118</v>
-      </c>
-      <c r="C27" t="s">
-        <v>122</v>
-      </c>
-      <c r="D27" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>83</v>
-      </c>
-      <c r="B28" t="s">
-        <v>119</v>
-      </c>
-      <c r="C28" t="s">
-        <v>122</v>
-      </c>
-      <c r="D28" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>84</v>
-      </c>
-      <c r="B29" t="s">
-        <v>119</v>
-      </c>
-      <c r="C29" t="s">
-        <v>122</v>
-      </c>
-      <c r="D29" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>85</v>
-      </c>
-      <c r="B30" t="s">
-        <v>118</v>
-      </c>
-      <c r="C30" t="s">
-        <v>122</v>
-      </c>
-      <c r="D30" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>86</v>
-      </c>
-      <c r="B31" t="s">
-        <v>119</v>
-      </c>
-      <c r="C31" t="s">
-        <v>122</v>
-      </c>
-      <c r="D31" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>87</v>
-      </c>
-      <c r="B32" t="s">
-        <v>118</v>
-      </c>
-      <c r="C32" t="s">
-        <v>122</v>
-      </c>
-      <c r="D32" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>88</v>
-      </c>
-      <c r="B33" t="s">
-        <v>119</v>
-      </c>
-      <c r="C33" t="s">
-        <v>122</v>
-      </c>
-      <c r="D33" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>89</v>
-      </c>
-      <c r="B34" t="s">
-        <v>119</v>
-      </c>
-      <c r="C34" t="s">
-        <v>122</v>
-      </c>
-      <c r="D34" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>90</v>
-      </c>
-      <c r="B35" t="s">
-        <v>118</v>
-      </c>
-      <c r="C35" t="s">
-        <v>122</v>
-      </c>
-      <c r="D35" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>91</v>
-      </c>
-      <c r="B36" t="s">
-        <v>119</v>
-      </c>
-      <c r="C36" t="s">
-        <v>122</v>
-      </c>
-      <c r="D36" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>92</v>
-      </c>
-      <c r="B37" t="s">
-        <v>118</v>
-      </c>
-      <c r="C37" t="s">
-        <v>122</v>
-      </c>
-      <c r="D37" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>93</v>
-      </c>
-      <c r="B38" t="s">
-        <v>119</v>
-      </c>
-      <c r="C38" t="s">
-        <v>122</v>
-      </c>
-      <c r="D38" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>94</v>
-      </c>
-      <c r="B39" t="s">
-        <v>118</v>
-      </c>
-      <c r="C39" t="s">
-        <v>122</v>
-      </c>
-      <c r="D39" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>95</v>
-      </c>
-      <c r="B40" t="s">
-        <v>119</v>
-      </c>
-      <c r="C40" t="s">
-        <v>122</v>
-      </c>
-      <c r="D40" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>96</v>
-      </c>
-      <c r="B41" t="s">
-        <v>119</v>
-      </c>
-      <c r="C41" t="s">
-        <v>122</v>
-      </c>
-      <c r="D41" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>97</v>
-      </c>
-      <c r="B42" t="s">
-        <v>119</v>
-      </c>
-      <c r="C42" t="s">
-        <v>122</v>
-      </c>
-      <c r="D42" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>98</v>
-      </c>
-      <c r="B43" t="s">
-        <v>119</v>
-      </c>
-      <c r="C43" t="s">
-        <v>122</v>
-      </c>
-      <c r="D43" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>99</v>
-      </c>
-      <c r="B44" t="s">
-        <v>119</v>
-      </c>
-      <c r="C44" t="s">
-        <v>122</v>
-      </c>
-      <c r="D44" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>100</v>
-      </c>
-      <c r="B45" t="s">
-        <v>119</v>
-      </c>
-      <c r="C45" t="s">
-        <v>122</v>
-      </c>
-      <c r="D45" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>101</v>
-      </c>
-      <c r="B46" t="s">
-        <v>118</v>
-      </c>
-      <c r="C46" t="s">
-        <v>122</v>
-      </c>
-      <c r="D46" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>102</v>
-      </c>
-      <c r="B47" t="s">
-        <v>118</v>
-      </c>
-      <c r="C47" t="s">
-        <v>122</v>
-      </c>
-      <c r="D47" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>103</v>
-      </c>
-      <c r="B48" t="s">
-        <v>119</v>
-      </c>
-      <c r="C48" t="s">
-        <v>122</v>
-      </c>
-      <c r="D48" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>104</v>
-      </c>
-      <c r="B49" t="s">
-        <v>119</v>
-      </c>
-      <c r="C49" t="s">
-        <v>122</v>
-      </c>
-      <c r="D49" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>105</v>
-      </c>
-      <c r="B50" t="s">
-        <v>119</v>
-      </c>
-      <c r="C50" t="s">
-        <v>122</v>
-      </c>
-      <c r="D50" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>106</v>
-      </c>
-      <c r="B51" t="s">
-        <v>119</v>
-      </c>
-      <c r="C51" t="s">
-        <v>122</v>
-      </c>
-      <c r="D51" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>107</v>
-      </c>
-      <c r="B52" t="s">
-        <v>119</v>
-      </c>
-      <c r="C52" t="s">
-        <v>122</v>
-      </c>
-      <c r="D52" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>108</v>
-      </c>
-      <c r="B53" t="s">
-        <v>118</v>
-      </c>
-      <c r="C53" t="s">
-        <v>122</v>
-      </c>
-      <c r="D53" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>109</v>
-      </c>
-      <c r="B54" t="s">
-        <v>121</v>
-      </c>
-      <c r="C54" t="s">
-        <v>122</v>
-      </c>
-      <c r="D54" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>110</v>
-      </c>
-      <c r="B55" t="s">
-        <v>118</v>
-      </c>
-      <c r="C55" t="s">
-        <v>122</v>
-      </c>
-      <c r="D55" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>111</v>
-      </c>
-      <c r="B56" t="s">
-        <v>119</v>
-      </c>
-      <c r="C56" t="s">
-        <v>122</v>
-      </c>
-      <c r="D56" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>112</v>
-      </c>
-      <c r="B57" t="s">
-        <v>118</v>
-      </c>
-      <c r="C57" t="s">
-        <v>122</v>
-      </c>
-      <c r="D57" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>113</v>
-      </c>
-      <c r="B58" t="s">
-        <v>119</v>
-      </c>
-      <c r="C58" t="s">
-        <v>122</v>
-      </c>
-      <c r="D58" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>114</v>
-      </c>
-      <c r="B59" t="s">
-        <v>118</v>
-      </c>
-      <c r="C59" t="s">
-        <v>122</v>
-      </c>
-      <c r="D59" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>115</v>
-      </c>
-      <c r="B60" t="s">
-        <v>118</v>
-      </c>
-      <c r="C60" t="s">
-        <v>122</v>
-      </c>
-      <c r="D60" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>116</v>
-      </c>
-      <c r="B61" t="s">
-        <v>118</v>
-      </c>
-      <c r="C61" t="s">
-        <v>122</v>
-      </c>
-      <c r="D61" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>117</v>
-      </c>
-      <c r="B62" t="s">
-        <v>118</v>
-      </c>
-      <c r="C62" t="s">
-        <v>122</v>
-      </c>
-      <c r="D62" t="s">
-        <v>123</v>
+      <c r="B16">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2121,96 +1384,997 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D62"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D5" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C6" t="s">
+        <v>134</v>
+      </c>
+      <c r="D6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C7" t="s">
+        <v>134</v>
+      </c>
+      <c r="D7" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C8" t="s">
+        <v>134</v>
+      </c>
+      <c r="D8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C9" t="s">
+        <v>134</v>
+      </c>
+      <c r="D9" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" t="s">
+        <v>130</v>
+      </c>
+      <c r="C10" t="s">
+        <v>134</v>
+      </c>
+      <c r="D10" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C11" t="s">
+        <v>134</v>
+      </c>
+      <c r="D11" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>79</v>
+      </c>
+      <c r="B12" t="s">
+        <v>130</v>
+      </c>
+      <c r="C12" t="s">
+        <v>134</v>
+      </c>
+      <c r="D12" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" t="s">
+        <v>131</v>
+      </c>
+      <c r="C13" t="s">
+        <v>134</v>
+      </c>
+      <c r="D13" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" t="s">
+        <v>131</v>
+      </c>
+      <c r="C14" t="s">
+        <v>134</v>
+      </c>
+      <c r="D14" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" t="s">
+        <v>131</v>
+      </c>
+      <c r="C15" t="s">
+        <v>134</v>
+      </c>
+      <c r="D15" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>83</v>
+      </c>
+      <c r="B16" t="s">
+        <v>131</v>
+      </c>
+      <c r="C16" t="s">
+        <v>134</v>
+      </c>
+      <c r="D16" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B17" t="s">
+        <v>133</v>
+      </c>
+      <c r="C17" t="s">
+        <v>134</v>
+      </c>
+      <c r="D17" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B18" t="s">
+        <v>130</v>
+      </c>
+      <c r="C18" t="s">
+        <v>134</v>
+      </c>
+      <c r="D18" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>86</v>
+      </c>
+      <c r="B19" t="s">
+        <v>131</v>
+      </c>
+      <c r="C19" t="s">
+        <v>134</v>
+      </c>
+      <c r="D19" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" t="s">
+        <v>131</v>
+      </c>
+      <c r="C20" t="s">
+        <v>134</v>
+      </c>
+      <c r="D20" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>88</v>
+      </c>
+      <c r="B21" t="s">
+        <v>131</v>
+      </c>
+      <c r="C21" t="s">
+        <v>134</v>
+      </c>
+      <c r="D21" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>89</v>
+      </c>
+      <c r="B22" t="s">
+        <v>131</v>
+      </c>
+      <c r="C22" t="s">
+        <v>134</v>
+      </c>
+      <c r="D22" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
+        <v>90</v>
+      </c>
+      <c r="B23" t="s">
+        <v>131</v>
+      </c>
+      <c r="C23" t="s">
+        <v>134</v>
+      </c>
+      <c r="D23" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" t="s">
+        <v>91</v>
+      </c>
+      <c r="B24" t="s">
+        <v>130</v>
+      </c>
+      <c r="C24" t="s">
+        <v>134</v>
+      </c>
+      <c r="D24" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" t="s">
+        <v>92</v>
+      </c>
+      <c r="B25" t="s">
+        <v>130</v>
+      </c>
+      <c r="C25" t="s">
+        <v>134</v>
+      </c>
+      <c r="D25" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" t="s">
+        <v>93</v>
+      </c>
+      <c r="B26" t="s">
+        <v>130</v>
+      </c>
+      <c r="C26" t="s">
+        <v>134</v>
+      </c>
+      <c r="D26" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" t="s">
+        <v>94</v>
+      </c>
+      <c r="B27" t="s">
+        <v>130</v>
+      </c>
+      <c r="C27" t="s">
+        <v>134</v>
+      </c>
+      <c r="D27" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" t="s">
+        <v>95</v>
+      </c>
+      <c r="B28" t="s">
+        <v>131</v>
+      </c>
+      <c r="C28" t="s">
+        <v>134</v>
+      </c>
+      <c r="D28" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" t="s">
+        <v>96</v>
+      </c>
+      <c r="B29" t="s">
+        <v>131</v>
+      </c>
+      <c r="C29" t="s">
+        <v>134</v>
+      </c>
+      <c r="D29" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" t="s">
+        <v>97</v>
+      </c>
+      <c r="B30" t="s">
+        <v>130</v>
+      </c>
+      <c r="C30" t="s">
+        <v>134</v>
+      </c>
+      <c r="D30" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" t="s">
+        <v>98</v>
+      </c>
+      <c r="B31" t="s">
+        <v>131</v>
+      </c>
+      <c r="C31" t="s">
+        <v>134</v>
+      </c>
+      <c r="D31" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" t="s">
+        <v>99</v>
+      </c>
+      <c r="B32" t="s">
+        <v>130</v>
+      </c>
+      <c r="C32" t="s">
+        <v>134</v>
+      </c>
+      <c r="D32" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" t="s">
+        <v>100</v>
+      </c>
+      <c r="B33" t="s">
+        <v>131</v>
+      </c>
+      <c r="C33" t="s">
+        <v>134</v>
+      </c>
+      <c r="D33" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" t="s">
+        <v>101</v>
+      </c>
+      <c r="B34" t="s">
+        <v>131</v>
+      </c>
+      <c r="C34" t="s">
+        <v>134</v>
+      </c>
+      <c r="D34" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" t="s">
+        <v>102</v>
+      </c>
+      <c r="B35" t="s">
+        <v>130</v>
+      </c>
+      <c r="C35" t="s">
+        <v>134</v>
+      </c>
+      <c r="D35" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" t="s">
+        <v>103</v>
+      </c>
+      <c r="B36" t="s">
+        <v>131</v>
+      </c>
+      <c r="C36" t="s">
+        <v>134</v>
+      </c>
+      <c r="D36" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" t="s">
+        <v>104</v>
+      </c>
+      <c r="B37" t="s">
+        <v>130</v>
+      </c>
+      <c r="C37" t="s">
+        <v>134</v>
+      </c>
+      <c r="D37" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" t="s">
+        <v>105</v>
+      </c>
+      <c r="B38" t="s">
+        <v>131</v>
+      </c>
+      <c r="C38" t="s">
+        <v>134</v>
+      </c>
+      <c r="D38" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>106</v>
+      </c>
+      <c r="B39" t="s">
+        <v>130</v>
+      </c>
+      <c r="C39" t="s">
+        <v>134</v>
+      </c>
+      <c r="D39" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" t="s">
+        <v>107</v>
+      </c>
+      <c r="B40" t="s">
+        <v>131</v>
+      </c>
+      <c r="C40" t="s">
+        <v>134</v>
+      </c>
+      <c r="D40" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" t="s">
+        <v>108</v>
+      </c>
+      <c r="B41" t="s">
+        <v>131</v>
+      </c>
+      <c r="C41" t="s">
+        <v>134</v>
+      </c>
+      <c r="D41" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" t="s">
+        <v>109</v>
+      </c>
+      <c r="B42" t="s">
+        <v>131</v>
+      </c>
+      <c r="C42" t="s">
+        <v>134</v>
+      </c>
+      <c r="D42" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" t="s">
+        <v>110</v>
+      </c>
+      <c r="B43" t="s">
+        <v>131</v>
+      </c>
+      <c r="C43" t="s">
+        <v>134</v>
+      </c>
+      <c r="D43" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" t="s">
+        <v>111</v>
+      </c>
+      <c r="B44" t="s">
+        <v>131</v>
+      </c>
+      <c r="C44" t="s">
+        <v>134</v>
+      </c>
+      <c r="D44" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" t="s">
+        <v>112</v>
+      </c>
+      <c r="B45" t="s">
+        <v>131</v>
+      </c>
+      <c r="C45" t="s">
+        <v>134</v>
+      </c>
+      <c r="D45" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" t="s">
+        <v>113</v>
+      </c>
+      <c r="B46" t="s">
+        <v>130</v>
+      </c>
+      <c r="C46" t="s">
+        <v>134</v>
+      </c>
+      <c r="D46" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" t="s">
+        <v>114</v>
+      </c>
+      <c r="B47" t="s">
+        <v>130</v>
+      </c>
+      <c r="C47" t="s">
+        <v>134</v>
+      </c>
+      <c r="D47" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" t="s">
+        <v>115</v>
+      </c>
+      <c r="B48" t="s">
+        <v>131</v>
+      </c>
+      <c r="C48" t="s">
+        <v>134</v>
+      </c>
+      <c r="D48" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" t="s">
+        <v>116</v>
+      </c>
+      <c r="B49" t="s">
+        <v>131</v>
+      </c>
+      <c r="C49" t="s">
+        <v>134</v>
+      </c>
+      <c r="D49" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" t="s">
+        <v>117</v>
+      </c>
+      <c r="B50" t="s">
+        <v>131</v>
+      </c>
+      <c r="C50" t="s">
+        <v>134</v>
+      </c>
+      <c r="D50" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" t="s">
+        <v>118</v>
+      </c>
+      <c r="B51" t="s">
+        <v>131</v>
+      </c>
+      <c r="C51" t="s">
+        <v>134</v>
+      </c>
+      <c r="D51" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" t="s">
+        <v>119</v>
+      </c>
+      <c r="B52" t="s">
+        <v>131</v>
+      </c>
+      <c r="C52" t="s">
+        <v>134</v>
+      </c>
+      <c r="D52" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" t="s">
+        <v>120</v>
+      </c>
+      <c r="B53" t="s">
+        <v>130</v>
+      </c>
+      <c r="C53" t="s">
+        <v>134</v>
+      </c>
+      <c r="D53" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" t="s">
+        <v>121</v>
+      </c>
+      <c r="B54" t="s">
+        <v>133</v>
+      </c>
+      <c r="C54" t="s">
+        <v>134</v>
+      </c>
+      <c r="D54" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" t="s">
+        <v>122</v>
+      </c>
+      <c r="B55" t="s">
+        <v>130</v>
+      </c>
+      <c r="C55" t="s">
+        <v>134</v>
+      </c>
+      <c r="D55" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" t="s">
+        <v>123</v>
+      </c>
+      <c r="B56" t="s">
+        <v>131</v>
+      </c>
+      <c r="C56" t="s">
+        <v>134</v>
+      </c>
+      <c r="D56" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" t="s">
+        <v>124</v>
+      </c>
+      <c r="B57" t="s">
+        <v>130</v>
+      </c>
+      <c r="C57" t="s">
+        <v>134</v>
+      </c>
+      <c r="D57" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" t="s">
+        <v>125</v>
+      </c>
+      <c r="B58" t="s">
+        <v>131</v>
+      </c>
+      <c r="C58" t="s">
+        <v>134</v>
+      </c>
+      <c r="D58" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" t="s">
+        <v>126</v>
+      </c>
+      <c r="B59" t="s">
+        <v>130</v>
+      </c>
+      <c r="C59" t="s">
+        <v>134</v>
+      </c>
+      <c r="D59" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" t="s">
+        <v>127</v>
+      </c>
+      <c r="B60" t="s">
+        <v>130</v>
+      </c>
+      <c r="C60" t="s">
+        <v>134</v>
+      </c>
+      <c r="D60" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" t="s">
+        <v>128</v>
+      </c>
+      <c r="B61" t="s">
+        <v>130</v>
+      </c>
+      <c r="C61" t="s">
+        <v>134</v>
+      </c>
+      <c r="D61" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" t="s">
+        <v>129</v>
+      </c>
+      <c r="B62" t="s">
+        <v>130</v>
+      </c>
+      <c r="C62" t="s">
+        <v>134</v>
+      </c>
+      <c r="D62" t="s">
+        <v>135</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="B2" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="C2" s="2">
-        <v>45812.627615740741</v>
+        <v>45812.62761574074</v>
       </c>
       <c r="D2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="B3" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="C3" s="2">
-        <v>45814.428437499999</v>
+        <v>45814.4284375</v>
       </c>
       <c r="D3" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="B4" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="C4" s="2">
-        <v>45814.644618055558</v>
+        <v>45814.64461805556</v>
       </c>
       <c r="D4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B5" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="C5" s="2">
-        <v>45814.677337962959</v>
+        <v>45814.67733796296</v>
       </c>
       <c r="D5" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="B6" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="C6" s="2">
-        <v>45812.627615740741</v>
+        <v>45812.62761574074</v>
       </c>
       <c r="D6" t="s">
-        <v>133</v>
+        <v>145</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/Monthly Dept Head Tracking Tool/Department Head Monthly Report Generation.xlsx
+++ b/Monthly Dept Head Tracking Tool/Department Head Monthly Report Generation.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="150">
   <si>
     <t>Category</t>
   </si>
@@ -214,6 +214,9 @@
   </si>
   <si>
     <t>Others Other Surgeries</t>
+  </si>
+  <si>
+    <t>Yelp For Help Candidate</t>
   </si>
   <si>
     <t>AnimalNumber</t>
@@ -1271,7 +1274,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1376,6 +1379,14 @@
       </c>
       <c r="B16">
         <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>65</v>
+      </c>
+      <c r="B18">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1390,870 +1401,870 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B14" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C14" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D14" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B15" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C15" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C16" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C17" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B18" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C18" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D18" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B19" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C19" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D19" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B20" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C20" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D20" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B21" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C21" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D21" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B22" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C22" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D22" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B23" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C23" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B24" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C24" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D24" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B25" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C25" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D25" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B26" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C26" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D26" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B27" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C27" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D27" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B28" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C28" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D28" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B29" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C29" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D29" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B30" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C30" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D30" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B31" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C31" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D31" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B32" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C32" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D32" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B33" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C33" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B34" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C34" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D34" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B35" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C35" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D35" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B36" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C36" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D36" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B37" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C37" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D37" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B38" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C38" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D38" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B39" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C39" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D39" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B40" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C40" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D40" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B41" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C41" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D41" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B42" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C42" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D42" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B43" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C43" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D43" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B44" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C44" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D44" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B45" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C45" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D45" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B46" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C46" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D46" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B47" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C47" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D47" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B48" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C48" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D48" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B49" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C49" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D49" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B50" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C50" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D50" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B51" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C51" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D51" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B52" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C52" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D52" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B53" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C53" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D53" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B54" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C54" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D54" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B55" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C55" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D55" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B56" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C56" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D56" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B57" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C57" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D57" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B58" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C58" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D58" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B59" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C59" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D59" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B60" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C60" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D60" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B61" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C61" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D61" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B62" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C62" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D62" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -2268,86 +2279,86 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C2" s="2">
         <v>45812.62761574074</v>
       </c>
       <c r="D2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C3" s="2">
         <v>45814.4284375</v>
       </c>
       <c r="D3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C4" s="2">
         <v>45814.64461805556</v>
       </c>
       <c r="D4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C5" s="2">
         <v>45814.67733796296</v>
       </c>
       <c r="D5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C6" s="2">
         <v>45812.62761574074</v>
       </c>
       <c r="D6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -2362,19 +2373,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
